--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/151.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/151.xlsx
@@ -426,13 +426,13 @@
         <v>-1.771361457434809</v>
       </c>
       <c r="E2">
-        <v>-18.62777575235744</v>
+        <v>-21.82926196461214</v>
       </c>
       <c r="F2">
-        <v>4.313757065894433</v>
+        <v>3.512353022056051</v>
       </c>
       <c r="G2">
-        <v>-11.91829614659853</v>
+        <v>-13.98686073190228</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-1.686831124583265</v>
       </c>
       <c r="E3">
-        <v>-21.0952687835529</v>
+        <v>-18.58244119906665</v>
       </c>
       <c r="F3">
-        <v>4.200317120285457</v>
+        <v>3.099791264030979</v>
       </c>
       <c r="G3">
-        <v>-11.29913143547972</v>
+        <v>-13.35345736441906</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-1.554032285149459</v>
       </c>
       <c r="E4">
-        <v>-21.2846676804497</v>
+        <v>-21.21703944961915</v>
       </c>
       <c r="F4">
-        <v>4.086960011416761</v>
+        <v>3.78487761390306</v>
       </c>
       <c r="G4">
-        <v>-12.59457107881531</v>
+        <v>-13.38371244010246</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-1.376689001879722</v>
       </c>
       <c r="E5">
-        <v>-22.57233473605676</v>
+        <v>-22.85185479418021</v>
       </c>
       <c r="F5">
-        <v>4.598770124706047</v>
+        <v>3.501940443802861</v>
       </c>
       <c r="G5">
-        <v>-10.88572044017216</v>
+        <v>-13.73404264543199</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.159026236378918</v>
       </c>
       <c r="E6">
-        <v>-20.03181553301361</v>
+        <v>-21.27330573916446</v>
       </c>
       <c r="F6">
-        <v>4.467061364395732</v>
+        <v>3.891218450870044</v>
       </c>
       <c r="G6">
-        <v>-10.23055023576823</v>
+        <v>-13.60634166180014</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-0.9068501302549312</v>
       </c>
       <c r="E7">
-        <v>-21.74433496307229</v>
+        <v>-23.8746921613447</v>
       </c>
       <c r="F7">
-        <v>4.760826953185326</v>
+        <v>3.268203327224536</v>
       </c>
       <c r="G7">
-        <v>-10.85742189690246</v>
+        <v>-12.76474967226155</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-0.6264587846990587</v>
       </c>
       <c r="E8">
-        <v>-22.57581713256866</v>
+        <v>-23.15409420640015</v>
       </c>
       <c r="F8">
-        <v>4.743628389168403</v>
+        <v>3.766211182848376</v>
       </c>
       <c r="G8">
-        <v>-10.36706058108008</v>
+        <v>-13.14978598175202</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.3252207651256516</v>
       </c>
       <c r="E9">
-        <v>-22.8169583734771</v>
+        <v>-23.8516060008536</v>
       </c>
       <c r="F9">
-        <v>4.635877670881854</v>
+        <v>4.056444613032434</v>
       </c>
       <c r="G9">
-        <v>-9.208449095428104</v>
+        <v>-12.78822144013498</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.01058953455905055</v>
       </c>
       <c r="E10">
-        <v>-24.90756462691019</v>
+        <v>-23.58441244897902</v>
       </c>
       <c r="F10">
-        <v>4.401911924900356</v>
+        <v>3.89437453067471</v>
       </c>
       <c r="G10">
-        <v>-10.51183404805795</v>
+        <v>-11.50940073540653</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.3121544560212817</v>
       </c>
       <c r="E11">
-        <v>-24.6216503634879</v>
+        <v>-25.05298751271851</v>
       </c>
       <c r="F11">
-        <v>4.675062762503882</v>
+        <v>4.111666897572659</v>
       </c>
       <c r="G11">
-        <v>-10.12254699809505</v>
+        <v>-10.10459059909004</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.6384100099159125</v>
       </c>
       <c r="E12">
-        <v>-24.83923448260845</v>
+        <v>-25.02885074625762</v>
       </c>
       <c r="F12">
-        <v>5.504861584175424</v>
+        <v>4.301961114078567</v>
       </c>
       <c r="G12">
-        <v>-9.562396071759283</v>
+        <v>-11.10984106263527</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.9649356605311625</v>
       </c>
       <c r="E13">
-        <v>-25.74742447332074</v>
+        <v>-25.14669522535923</v>
       </c>
       <c r="F13">
-        <v>5.315551468144043</v>
+        <v>4.497966095459375</v>
       </c>
       <c r="G13">
-        <v>-8.997216426749366</v>
+        <v>-10.80355269988744</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.288005811291262</v>
       </c>
       <c r="E14">
-        <v>-26.23876843162699</v>
+        <v>-26.50576273064522</v>
       </c>
       <c r="F14">
-        <v>5.893140580154832</v>
+        <v>4.519407557313437</v>
       </c>
       <c r="G14">
-        <v>-9.162982062991754</v>
+        <v>-9.743575608032517</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.605407604000924</v>
       </c>
       <c r="E15">
-        <v>-26.46754693849449</v>
+        <v>-27.43348402975261</v>
       </c>
       <c r="F15">
-        <v>5.926485681587123</v>
+        <v>4.750391180644858</v>
       </c>
       <c r="G15">
-        <v>-8.16267755448219</v>
+        <v>-10.91593247876354</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.915787278060633</v>
       </c>
       <c r="E16">
-        <v>-26.4841981374207</v>
+        <v>-27.75250143817096</v>
       </c>
       <c r="F16">
-        <v>6.089829793010352</v>
+        <v>5.210294135739921</v>
       </c>
       <c r="G16">
-        <v>-8.692295319309254</v>
+        <v>-10.28505836807233</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.219307502296018</v>
       </c>
       <c r="E17">
-        <v>-28.58974835507909</v>
+        <v>-27.9629396253074</v>
       </c>
       <c r="F17">
-        <v>6.52728730495916</v>
+        <v>4.983044792660321</v>
       </c>
       <c r="G17">
-        <v>-7.059348868790506</v>
+        <v>-9.026246600583235</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.516337394393994</v>
       </c>
       <c r="E18">
-        <v>-29.35291396569575</v>
+        <v>-28.56093820344229</v>
       </c>
       <c r="F18">
-        <v>6.066201441212899</v>
+        <v>5.59867750601208</v>
       </c>
       <c r="G18">
-        <v>-6.633814655718127</v>
+        <v>-8.764011667326487</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.810138210721575</v>
       </c>
       <c r="E19">
-        <v>-30.62327545788249</v>
+        <v>-28.66606672753036</v>
       </c>
       <c r="F19">
-        <v>6.299171489576231</v>
+        <v>5.273034682827955</v>
       </c>
       <c r="G19">
-        <v>-7.092368249999197</v>
+        <v>-8.495377449542326</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>3.104443217703276</v>
       </c>
       <c r="E20">
-        <v>-30.05660259869566</v>
+        <v>-30.31612038712723</v>
       </c>
       <c r="F20">
-        <v>7.299408561108579</v>
+        <v>5.354678574047875</v>
       </c>
       <c r="G20">
-        <v>-6.35208060923507</v>
+        <v>-7.784149777521923</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.401648403981308</v>
       </c>
       <c r="E21">
-        <v>-30.16798041691431</v>
+        <v>-31.36192391022162</v>
       </c>
       <c r="F21">
-        <v>6.707026464018596</v>
+        <v>5.826839709969565</v>
       </c>
       <c r="G21">
-        <v>-5.298883514644571</v>
+        <v>-7.991121774091617</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.70190363209525</v>
       </c>
       <c r="E22">
-        <v>-30.99718929245883</v>
+        <v>-30.28259609404845</v>
       </c>
       <c r="F22">
-        <v>7.183239973274781</v>
+        <v>6.370084709460286</v>
       </c>
       <c r="G22">
-        <v>-5.947591534155839</v>
+        <v>-7.549961786073879</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>4.0028420041071</v>
       </c>
       <c r="E23">
-        <v>-32.25018182258916</v>
+        <v>-32.28801722292324</v>
       </c>
       <c r="F23">
-        <v>7.491992385115824</v>
+        <v>6.106960430900245</v>
       </c>
       <c r="G23">
-        <v>-5.492424627961443</v>
+        <v>-6.241329618764293</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>4.299087273418916</v>
       </c>
       <c r="E24">
-        <v>-30.66752770588545</v>
+        <v>-32.02034365280385</v>
       </c>
       <c r="F24">
-        <v>8.328249159059592</v>
+        <v>6.224578661688942</v>
       </c>
       <c r="G24">
-        <v>-6.796925234438018</v>
+        <v>-7.02984859749006</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.582641967255022</v>
       </c>
       <c r="E25">
-        <v>-31.9972257929947</v>
+        <v>-32.53314804943245</v>
       </c>
       <c r="F25">
-        <v>8.043918674987884</v>
+        <v>5.906059798168893</v>
       </c>
       <c r="G25">
-        <v>-4.269886507946143</v>
+        <v>-7.14573093354671</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.843610796781429</v>
       </c>
       <c r="E26">
-        <v>-32.18942328682824</v>
+        <v>-31.96859678031821</v>
       </c>
       <c r="F26">
-        <v>7.720688057680712</v>
+        <v>6.216112746832331</v>
       </c>
       <c r="G26">
-        <v>-4.422145118388304</v>
+        <v>-6.566673481636168</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>5.071501995334822</v>
       </c>
       <c r="E27">
-        <v>-31.18075098635975</v>
+        <v>-31.8499847248723</v>
       </c>
       <c r="F27">
-        <v>7.939126885064136</v>
+        <v>6.245256368797623</v>
       </c>
       <c r="G27">
-        <v>-4.547793563785802</v>
+        <v>-6.592340141202138</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>5.259666834612006</v>
       </c>
       <c r="E28">
-        <v>-31.97622273054712</v>
+        <v>-32.74735619118027</v>
       </c>
       <c r="F28">
-        <v>7.747687864807559</v>
+        <v>5.745073220374031</v>
       </c>
       <c r="G28">
-        <v>-4.883559024015304</v>
+        <v>-4.980624219226735</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>5.402691240730783</v>
       </c>
       <c r="E29">
-        <v>-32.71453834004669</v>
+        <v>-33.62547485024464</v>
       </c>
       <c r="F29">
-        <v>7.523889500328022</v>
+        <v>6.201374434001722</v>
       </c>
       <c r="G29">
-        <v>-4.065589432172179</v>
+        <v>-6.055862926017703</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.498308377846879</v>
       </c>
       <c r="E30">
-        <v>-31.41945817248907</v>
+        <v>-32.44419070602577</v>
       </c>
       <c r="F30">
-        <v>7.425338630416965</v>
+        <v>6.264597090918186</v>
       </c>
       <c r="G30">
-        <v>-5.062990592243803</v>
+        <v>-7.407863239891741</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.549546436968385</v>
       </c>
       <c r="E31">
-        <v>-30.89771230393234</v>
+        <v>-31.35242090751652</v>
       </c>
       <c r="F31">
-        <v>7.460151598887017</v>
+        <v>6.573622864002153</v>
       </c>
       <c r="G31">
-        <v>-5.89130232835161</v>
+        <v>-6.268985916199364</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.562237344725515</v>
       </c>
       <c r="E32">
-        <v>-32.45480544909975</v>
+        <v>-33.11139795241989</v>
       </c>
       <c r="F32">
-        <v>8.062492328893455</v>
+        <v>6.032763562631493</v>
       </c>
       <c r="G32">
-        <v>-4.98046862358639</v>
+        <v>-6.037793968464361</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.545107848416474</v>
       </c>
       <c r="E33">
-        <v>-29.63049583694391</v>
+        <v>-32.24991690685971</v>
       </c>
       <c r="F33">
-        <v>7.626325413358209</v>
+        <v>6.262078854013676</v>
       </c>
       <c r="G33">
-        <v>-3.448354769102763</v>
+        <v>-6.171775056984204</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.50880859866312</v>
       </c>
       <c r="E34">
-        <v>-31.6020236021083</v>
+        <v>-32.21185734706224</v>
       </c>
       <c r="F34">
-        <v>7.425968189643092</v>
+        <v>5.745200788954063</v>
       </c>
       <c r="G34">
-        <v>-5.405211616274883</v>
+        <v>-5.875653379587476</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.462713810554079</v>
       </c>
       <c r="E35">
-        <v>-29.25533893625247</v>
+        <v>-31.86781106280349</v>
       </c>
       <c r="F35">
-        <v>7.380833763334159</v>
+        <v>6.37706618993108</v>
       </c>
       <c r="G35">
-        <v>-5.187410825246231</v>
+        <v>-6.76880215008191</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>5.418884377273459</v>
       </c>
       <c r="E36">
-        <v>-31.82323276467199</v>
+        <v>-30.22824534900839</v>
       </c>
       <c r="F36">
-        <v>7.475723249324842</v>
+        <v>5.976287129843429</v>
       </c>
       <c r="G36">
-        <v>-5.141841165898163</v>
+        <v>-7.39374376316675</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>5.386783618725159</v>
       </c>
       <c r="E37">
-        <v>-28.63376059395964</v>
+        <v>-30.59630839516682</v>
       </c>
       <c r="F37">
-        <v>7.48653178719657</v>
+        <v>6.269703147589042</v>
       </c>
       <c r="G37">
-        <v>-6.871856122173883</v>
+        <v>-7.701886031416572</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>5.371829126193814</v>
       </c>
       <c r="E38">
-        <v>-30.26342027086297</v>
+        <v>-29.79082645918549</v>
       </c>
       <c r="F38">
-        <v>7.589950143966477</v>
+        <v>5.303659425709453</v>
       </c>
       <c r="G38">
-        <v>-7.284333543639376</v>
+        <v>-6.935839035811377</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>5.378582353504846</v>
       </c>
       <c r="E39">
-        <v>-28.50835356326522</v>
+        <v>-29.25902964256872</v>
       </c>
       <c r="F39">
-        <v>7.179122987282868</v>
+        <v>6.588989079324083</v>
       </c>
       <c r="G39">
-        <v>-5.482062620423524</v>
+        <v>-7.285214148752822</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>5.407698036354222</v>
       </c>
       <c r="E40">
-        <v>-27.52763100437207</v>
+        <v>-28.13297929582141</v>
       </c>
       <c r="F40">
-        <v>7.780595588251172</v>
+        <v>6.233467043920981</v>
       </c>
       <c r="G40">
-        <v>-4.474862245555658</v>
+        <v>-7.887041532882471</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>5.456302359207894</v>
       </c>
       <c r="E41">
-        <v>-29.5310686616315</v>
+        <v>-28.22762893105573</v>
       </c>
       <c r="F41">
-        <v>7.653601895197591</v>
+        <v>6.199439367748782</v>
       </c>
       <c r="G41">
-        <v>-6.279020179728895</v>
+        <v>-7.248285013262252</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>5.519059145953855</v>
       </c>
       <c r="E42">
-        <v>-26.48629029241224</v>
+        <v>-27.93106369676741</v>
       </c>
       <c r="F42">
-        <v>7.67497708765943</v>
+        <v>6.213085892342502</v>
       </c>
       <c r="G42">
-        <v>-6.85851462365062</v>
+        <v>-7.53355472238125</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>5.588061215877455</v>
       </c>
       <c r="E43">
-        <v>-26.76183435035696</v>
+        <v>-27.59820274330761</v>
       </c>
       <c r="F43">
-        <v>7.748951953464231</v>
+        <v>6.731453361992348</v>
       </c>
       <c r="G43">
-        <v>-6.614186431215789</v>
+        <v>-8.098833683757345</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>5.655842756991323</v>
       </c>
       <c r="E44">
-        <v>-26.83145963822489</v>
+        <v>-25.77008495725513</v>
       </c>
       <c r="F44">
-        <v>7.690860204240708</v>
+        <v>5.970427258836025</v>
       </c>
       <c r="G44">
-        <v>-7.472607579003268</v>
+        <v>-7.721918142474703</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>5.71663440414834</v>
       </c>
       <c r="E45">
-        <v>-24.39609613011386</v>
+        <v>-25.99590637059563</v>
       </c>
       <c r="F45">
-        <v>7.658210931426768</v>
+        <v>6.169112837132293</v>
       </c>
       <c r="G45">
-        <v>-6.491153316794314</v>
+        <v>-7.890775828250769</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>5.764217047613349</v>
       </c>
       <c r="E46">
-        <v>-24.85481243319483</v>
+        <v>-24.9711579873999</v>
       </c>
       <c r="F46">
-        <v>8.221721111059576</v>
+        <v>6.61268370051376</v>
       </c>
       <c r="G46">
-        <v>-7.742748095007797</v>
+        <v>-8.839574869260352</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>5.794140315012392</v>
       </c>
       <c r="E47">
-        <v>-25.7081943029923</v>
+        <v>-22.94474738149955</v>
       </c>
       <c r="F47">
-        <v>6.947799733316301</v>
+        <v>6.639812732955444</v>
       </c>
       <c r="G47">
-        <v>-6.730936130203726</v>
+        <v>-8.486376076221047</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>5.804344775610796</v>
       </c>
       <c r="E48">
-        <v>-24.12377181718859</v>
+        <v>-24.8293488238497</v>
       </c>
       <c r="F48">
-        <v>7.676895586564314</v>
+        <v>6.575738514348902</v>
       </c>
       <c r="G48">
-        <v>-6.323662886325967</v>
+        <v>-7.802414057262081</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>5.792508730242539</v>
       </c>
       <c r="E49">
-        <v>-23.13944912145934</v>
+        <v>-25.30947575203895</v>
       </c>
       <c r="F49">
-        <v>7.237958610434106</v>
+        <v>6.481766859440521</v>
       </c>
       <c r="G49">
-        <v>-6.983603586851982</v>
+        <v>-8.459431546076919</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>5.756955098874753</v>
       </c>
       <c r="E50">
-        <v>-22.29744730684315</v>
+        <v>-24.36042534035544</v>
       </c>
       <c r="F50">
-        <v>7.497989765112093</v>
+        <v>6.20177039362026</v>
       </c>
       <c r="G50">
-        <v>-7.234172157628339</v>
+        <v>-8.475596939945181</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>5.696573825215489</v>
       </c>
       <c r="E51">
-        <v>-21.52948604225238</v>
+        <v>-21.5687614973209</v>
       </c>
       <c r="F51">
-        <v>7.705729399120958</v>
+        <v>6.060205717951436</v>
       </c>
       <c r="G51">
-        <v>-7.636410061740867</v>
+        <v>-8.517730253023485</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>5.609736070052093</v>
       </c>
       <c r="E52">
-        <v>-23.35539393298911</v>
+        <v>-21.50652215055948</v>
       </c>
       <c r="F52">
-        <v>8.242251368770559</v>
+        <v>6.416120399503466</v>
       </c>
       <c r="G52">
-        <v>-7.712774415695235</v>
+        <v>-9.35664235594804</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>5.497277850838936</v>
       </c>
       <c r="E53">
-        <v>-21.42727385542525</v>
+        <v>-21.13068145029288</v>
       </c>
       <c r="F53">
-        <v>7.254978247092025</v>
+        <v>6.397472192531644</v>
       </c>
       <c r="G53">
-        <v>-7.352719482844101</v>
+        <v>-10.00494317835798</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>5.359086875742413</v>
       </c>
       <c r="E54">
-        <v>-21.41773236069109</v>
+        <v>-21.90615092478837</v>
       </c>
       <c r="F54">
-        <v>7.037230278122535</v>
+        <v>6.39890029793407</v>
       </c>
       <c r="G54">
-        <v>-7.573274647761426</v>
+        <v>-8.575231118495086</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>5.193334802132748</v>
       </c>
       <c r="E55">
-        <v>-21.28902860091909</v>
+        <v>-21.39741309781867</v>
       </c>
       <c r="F55">
-        <v>7.506654488145376</v>
+        <v>6.278836726572309</v>
       </c>
       <c r="G55">
-        <v>-7.720444949709727</v>
+        <v>-9.602850938249176</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>5.001896992888991</v>
       </c>
       <c r="E56">
-        <v>-20.77895487411712</v>
+        <v>-21.73392852980266</v>
       </c>
       <c r="F56">
-        <v>7.387840094827037</v>
+        <v>6.872366940882572</v>
       </c>
       <c r="G56">
-        <v>-7.810074659639954</v>
+        <v>-8.322374960751093</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>4.785179856346072</v>
       </c>
       <c r="E57">
-        <v>-17.48284166899814</v>
+        <v>-20.53250626167168</v>
       </c>
       <c r="F57">
-        <v>7.408883940327756</v>
+        <v>6.558067780912383</v>
       </c>
       <c r="G57">
-        <v>-7.949647259575628</v>
+        <v>-9.287385743266487</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>4.543858127634679</v>
       </c>
       <c r="E58">
-        <v>-20.01715233417677</v>
+        <v>-19.99167513940962</v>
       </c>
       <c r="F58">
-        <v>7.618898271224709</v>
+        <v>6.024455037581415</v>
       </c>
       <c r="G58">
-        <v>-8.640925584176385</v>
+        <v>-9.854127965770939</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>4.27908451832069</v>
       </c>
       <c r="E59">
-        <v>-19.46446113848862</v>
+        <v>-19.1481743998969</v>
       </c>
       <c r="F59">
-        <v>6.875226465157036</v>
+        <v>5.830183000807263</v>
       </c>
       <c r="G59">
-        <v>-7.464953597716473</v>
+        <v>-9.329813694897785</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>3.992634014064493</v>
       </c>
       <c r="E60">
-        <v>-18.52491146527321</v>
+        <v>-21.00219505727325</v>
       </c>
       <c r="F60">
-        <v>7.755638535139629</v>
+        <v>6.019554416026453</v>
       </c>
       <c r="G60">
-        <v>-9.230321869806069</v>
+        <v>-9.597368674836144</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>3.687134591261627</v>
       </c>
       <c r="E61">
-        <v>-19.65144635873934</v>
+        <v>-18.34970933439045</v>
       </c>
       <c r="F61">
-        <v>6.867902040581482</v>
+        <v>5.980679133813072</v>
       </c>
       <c r="G61">
-        <v>-9.04216701408159</v>
+        <v>-10.34555196671143</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>3.365687666644553</v>
       </c>
       <c r="E62">
-        <v>-19.75287059108913</v>
+        <v>-17.87375313076227</v>
       </c>
       <c r="F62">
-        <v>6.921295289896327</v>
+        <v>5.431461605348166</v>
       </c>
       <c r="G62">
-        <v>-9.634115730322055</v>
+        <v>-10.21785760417066</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>3.030919364355925</v>
       </c>
       <c r="E63">
-        <v>-18.51094112295955</v>
+        <v>-17.44185897922873</v>
       </c>
       <c r="F63">
-        <v>7.127300322563731</v>
+        <v>6.071102062767861</v>
       </c>
       <c r="G63">
-        <v>-9.027805867532233</v>
+        <v>-9.302961860028757</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>2.687330412797249</v>
       </c>
       <c r="E64">
-        <v>-16.84007006834941</v>
+        <v>-17.74445614089527</v>
       </c>
       <c r="F64">
-        <v>6.755471046469117</v>
+        <v>5.775722814277612</v>
       </c>
       <c r="G64">
-        <v>-10.22827920152829</v>
+        <v>-9.286137667598181</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>2.340509828429488</v>
       </c>
       <c r="E65">
-        <v>-18.05722878365705</v>
+        <v>-17.61764528325848</v>
       </c>
       <c r="F65">
-        <v>6.176841505000412</v>
+        <v>6.047173841970594</v>
       </c>
       <c r="G65">
-        <v>-8.747432455265816</v>
+        <v>-9.532379355354712</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>1.995528291305802</v>
       </c>
       <c r="E66">
-        <v>-17.868871435782</v>
+        <v>-18.23747563458435</v>
       </c>
       <c r="F66">
-        <v>5.958248601280067</v>
+        <v>5.446122051642912</v>
       </c>
       <c r="G66">
-        <v>-7.869753864076396</v>
+        <v>-9.606790487440909</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>1.657450064136128</v>
       </c>
       <c r="E67">
-        <v>-16.47070961438779</v>
+        <v>-18.56746553552329</v>
       </c>
       <c r="F67">
-        <v>5.72673316607605</v>
+        <v>5.663316671187332</v>
       </c>
       <c r="G67">
-        <v>-9.001354608673456</v>
+        <v>-9.878258532206686</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>1.331219736394958</v>
       </c>
       <c r="E68">
-        <v>-16.25069823319913</v>
+        <v>-16.67868884013807</v>
       </c>
       <c r="F68">
-        <v>6.028861952164308</v>
+        <v>5.361858862695341</v>
       </c>
       <c r="G68">
-        <v>-8.495595945547919</v>
+        <v>-9.910334407936684</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>1.0210046530049</v>
       </c>
       <c r="E69">
-        <v>-17.77475163200658</v>
+        <v>-17.94045755289526</v>
       </c>
       <c r="F69">
-        <v>5.943439048852817</v>
+        <v>5.341570488265975</v>
       </c>
       <c r="G69">
-        <v>-8.365915255683587</v>
+        <v>-9.780306110790731</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>0.7302891851446512</v>
       </c>
       <c r="E70">
-        <v>-15.02873027849536</v>
+        <v>-17.78735437516993</v>
       </c>
       <c r="F70">
-        <v>5.988275262896743</v>
+        <v>5.006292095452486</v>
       </c>
       <c r="G70">
-        <v>-9.077742136446599</v>
+        <v>-9.809541538448034</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>0.4624168023718107</v>
       </c>
       <c r="E71">
-        <v>-18.29755942771812</v>
+        <v>-17.74120922503177</v>
       </c>
       <c r="F71">
-        <v>5.718099921004073</v>
+        <v>4.866488528882014</v>
       </c>
       <c r="G71">
-        <v>-8.274742831532059</v>
+        <v>-9.118233418937425</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>0.2200520150177344</v>
       </c>
       <c r="E72">
-        <v>-16.93354682881575</v>
+        <v>-18.72196348324298</v>
       </c>
       <c r="F72">
-        <v>6.013033507831615</v>
+        <v>4.737420603851823</v>
       </c>
       <c r="G72">
-        <v>-8.658812461725066</v>
+        <v>-9.031718932359651</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.00822328536382072</v>
       </c>
       <c r="E73">
-        <v>-17.36701236082995</v>
+        <v>-19.03436931961013</v>
       </c>
       <c r="F73">
-        <v>5.366560676073631</v>
+        <v>5.132611497440188</v>
       </c>
       <c r="G73">
-        <v>-8.480539584435313</v>
+        <v>-8.986685581388945</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-0.1696099395583919</v>
       </c>
       <c r="E74">
-        <v>-16.49071641255368</v>
+        <v>-19.82898518221006</v>
       </c>
       <c r="F74">
-        <v>5.102750509304072</v>
+        <v>5.186662470472856</v>
       </c>
       <c r="G74">
-        <v>-7.173761322627718</v>
+        <v>-8.268270715002783</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-0.3104153400223759</v>
       </c>
       <c r="E75">
-        <v>-16.33698377694128</v>
+        <v>-20.05106154754621</v>
       </c>
       <c r="F75">
-        <v>5.41758810808608</v>
+        <v>5.113645197385691</v>
       </c>
       <c r="G75">
-        <v>-7.776674565694248</v>
+        <v>-10.02835204586616</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-0.4116042523547159</v>
       </c>
       <c r="E76">
-        <v>-17.37202991003045</v>
+        <v>-17.66595957244631</v>
       </c>
       <c r="F76">
-        <v>5.233884382636845</v>
+        <v>4.705004930645472</v>
       </c>
       <c r="G76">
-        <v>-6.837674739480907</v>
+        <v>-9.03817780670677</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.4717982043224137</v>
       </c>
       <c r="E77">
-        <v>-17.87507544517251</v>
+        <v>-20.16215860037639</v>
       </c>
       <c r="F77">
-        <v>5.198460079023527</v>
+        <v>4.369501221898423</v>
       </c>
       <c r="G77">
-        <v>-8.146482365704076</v>
+        <v>-8.407353354198644</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.4905524048930422</v>
       </c>
       <c r="E78">
-        <v>-18.76173707045234</v>
+        <v>-18.54870859618352</v>
       </c>
       <c r="F78">
-        <v>4.813675136749128</v>
+        <v>4.096713209217323</v>
       </c>
       <c r="G78">
-        <v>-6.705948132473307</v>
+        <v>-9.469680933386455</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.4687787157333305</v>
       </c>
       <c r="E79">
-        <v>-17.45104725299029</v>
+        <v>-19.28559547213366</v>
       </c>
       <c r="F79">
-        <v>5.133519388113656</v>
+        <v>4.799385799050837</v>
       </c>
       <c r="G79">
-        <v>-6.829848609826071</v>
+        <v>-8.633483477804102</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.4086465709262649</v>
       </c>
       <c r="E80">
-        <v>-20.34304396613877</v>
+        <v>-20.64485317332798</v>
       </c>
       <c r="F80">
-        <v>4.901155704689173</v>
+        <v>4.69620104188852</v>
       </c>
       <c r="G80">
-        <v>-6.239075137252049</v>
+        <v>-7.438694350498974</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-0.3130205079811198</v>
       </c>
       <c r="E81">
-        <v>-20.59817819173092</v>
+        <v>-20.4561788322724</v>
       </c>
       <c r="F81">
-        <v>4.658101111564159</v>
+        <v>4.630541328073019</v>
       </c>
       <c r="G81">
-        <v>-7.19305849257613</v>
+        <v>-9.130131519605566</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.1856116444491119</v>
       </c>
       <c r="E82">
-        <v>-22.14787633884381</v>
+        <v>-21.42939770973485</v>
       </c>
       <c r="F82">
-        <v>5.135220854759007</v>
+        <v>4.501264654457323</v>
       </c>
       <c r="G82">
-        <v>-5.816096665335987</v>
+        <v>-7.954940821892922</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.03054227350737491</v>
       </c>
       <c r="E83">
-        <v>-22.50282718851303</v>
+        <v>-22.03027186886461</v>
       </c>
       <c r="F83">
-        <v>4.887812362564879</v>
+        <v>4.537674715279972</v>
       </c>
       <c r="G83">
-        <v>-5.27281296852281</v>
+        <v>-7.479013484621758</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.1478411284628185</v>
       </c>
       <c r="E84">
-        <v>-23.00294732944613</v>
+        <v>-23.7201308149889</v>
       </c>
       <c r="F84">
-        <v>4.73477148489767</v>
+        <v>4.304630113850387</v>
       </c>
       <c r="G84">
-        <v>-6.241640810044983</v>
+        <v>-6.923599948952691</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.3450801438947397</v>
       </c>
       <c r="E85">
-        <v>-25.15490534873513</v>
+        <v>-24.05151548592221</v>
       </c>
       <c r="F85">
-        <v>5.48398175542046</v>
+        <v>4.714602395374308</v>
       </c>
       <c r="G85">
-        <v>-5.431103392937523</v>
+        <v>-7.819324323876678</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.5571573289050854</v>
       </c>
       <c r="E86">
-        <v>-25.30467556959082</v>
+        <v>-26.81354499505055</v>
       </c>
       <c r="F86">
-        <v>5.423552353386237</v>
+        <v>4.916616353895023</v>
       </c>
       <c r="G86">
-        <v>-4.607188061305867</v>
+        <v>-6.728218172315985</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.7816489974857258</v>
       </c>
       <c r="E87">
-        <v>-26.46514231879642</v>
+        <v>-26.74722549320822</v>
       </c>
       <c r="F87">
-        <v>5.040029843033705</v>
+        <v>4.063257106553056</v>
       </c>
       <c r="G87">
-        <v>-4.918660738368197</v>
+        <v>-7.264589450043163</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.016349402048975</v>
       </c>
       <c r="E88">
-        <v>-26.19788083981173</v>
+        <v>-27.08716445154201</v>
       </c>
       <c r="F88">
-        <v>4.551909380729679</v>
+        <v>4.212225730068103</v>
       </c>
       <c r="G88">
-        <v>-4.806069084577583</v>
+        <v>-6.626802920265951</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.259506066205517</v>
       </c>
       <c r="E89">
-        <v>-28.55595235355985</v>
+        <v>-28.90113528479452</v>
       </c>
       <c r="F89">
-        <v>4.809700629950497</v>
+        <v>3.853989963053428</v>
       </c>
       <c r="G89">
-        <v>-5.907355163671537</v>
+        <v>-7.639290236360033</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.509293000237418</v>
       </c>
       <c r="E90">
-        <v>-31.18006039407358</v>
+        <v>-30.32798951750134</v>
       </c>
       <c r="F90">
-        <v>5.193927252595408</v>
+        <v>4.327224663129146</v>
       </c>
       <c r="G90">
-        <v>-4.452585584621902</v>
+        <v>-6.963710518706501</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>1.763959823916559</v>
       </c>
       <c r="E91">
-        <v>-32.85469234634708</v>
+        <v>-30.61981796797764</v>
       </c>
       <c r="F91">
-        <v>5.521937549816734</v>
+        <v>4.211864561880482</v>
       </c>
       <c r="G91">
-        <v>-5.190128783133973</v>
+        <v>-6.835277904510475</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.021449979179745</v>
       </c>
       <c r="E92">
-        <v>-34.64973868672154</v>
+        <v>-33.99332732236171</v>
       </c>
       <c r="F92">
-        <v>5.199709257066949</v>
+        <v>4.476392094820865</v>
       </c>
       <c r="G92">
-        <v>-4.595856063924941</v>
+        <v>-6.529171621767304</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.279141288252795</v>
       </c>
       <c r="E93">
-        <v>-36.53143964146978</v>
+        <v>-34.3933070533262</v>
       </c>
       <c r="F93">
-        <v>4.966618267062807</v>
+        <v>3.927658332919194</v>
       </c>
       <c r="G93">
-        <v>-5.056227147707071</v>
+        <v>-5.712208435768118</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.532321690578792</v>
       </c>
       <c r="E94">
-        <v>-36.59886861944399</v>
+        <v>-36.43866705871164</v>
       </c>
       <c r="F94">
-        <v>4.205855584740575</v>
+        <v>4.018195576575569</v>
       </c>
       <c r="G94">
-        <v>-3.401368196263887</v>
+        <v>-6.629421561787514</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.778700375300685</v>
       </c>
       <c r="E95">
-        <v>-39.27504052562391</v>
+        <v>-37.86220644844484</v>
       </c>
       <c r="F95">
-        <v>4.754920693603365</v>
+        <v>3.822419224597934</v>
       </c>
       <c r="G95">
-        <v>-6.438108445618572</v>
+        <v>-5.696129116083878</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>3.014118746626699</v>
       </c>
       <c r="E96">
-        <v>-41.74755110601986</v>
+        <v>-41.1163339068017</v>
       </c>
       <c r="F96">
-        <v>4.820648333545895</v>
+        <v>3.275617215479592</v>
       </c>
       <c r="G96">
-        <v>-3.803420709826215</v>
+        <v>-6.540781704973528</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>3.234082252812452</v>
       </c>
       <c r="E97">
-        <v>-42.81762272132136</v>
+        <v>-43.51368313985535</v>
       </c>
       <c r="F97">
-        <v>3.675135500380182</v>
+        <v>3.689897007498069</v>
       </c>
       <c r="G97">
-        <v>-5.84133626452739</v>
+        <v>-8.05529338882485</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>3.433807819727093</v>
       </c>
       <c r="E98">
-        <v>-46.4090286595325</v>
+        <v>-44.74066864375962</v>
       </c>
       <c r="F98">
-        <v>4.789309537963184</v>
+        <v>3.256329508872807</v>
       </c>
       <c r="G98">
-        <v>-4.318283373184749</v>
+        <v>-7.186007030577483</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>3.609036269055818</v>
       </c>
       <c r="E99">
-        <v>-46.54792601429577</v>
+        <v>-46.32699308864655</v>
       </c>
       <c r="F99">
-        <v>3.787425672034071</v>
+        <v>2.886900841511506</v>
       </c>
       <c r="G99">
-        <v>-5.876305557058712</v>
+        <v>-7.653091900713254</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>3.754881736249129</v>
       </c>
       <c r="E100">
-        <v>-50.9921364418684</v>
+        <v>-47.7698101922304</v>
       </c>
       <c r="F100">
-        <v>4.469026251875172</v>
+        <v>3.316707552128058</v>
       </c>
       <c r="G100">
-        <v>-5.046782161283531</v>
+        <v>-8.004208360608356</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>3.868330208638429</v>
       </c>
       <c r="E101">
-        <v>-51.70822969729382</v>
+        <v>-51.077216279406</v>
       </c>
       <c r="F101">
-        <v>3.836064092456847</v>
+        <v>2.395407267143281</v>
       </c>
       <c r="G101">
-        <v>-6.069605000551217</v>
+        <v>-7.857124132844077</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.943811629550324</v>
       </c>
       <c r="E102">
-        <v>-55.10663546965356</v>
+        <v>-53.34391790521986</v>
       </c>
       <c r="F102">
-        <v>3.68015043663673</v>
+        <v>1.700960365619566</v>
       </c>
       <c r="G102">
-        <v>-6.65410829987386</v>
+        <v>-7.642815967359357</v>
       </c>
     </row>
   </sheetData>
